--- a/pipeline/samples/tg_company/goods_receipts.xlsx
+++ b/pipeline/samples/tg_company/goods_receipts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,6 +618,46 @@
         <v>25000</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GR-2026-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PO-2026-010</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GR-2026-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PO-2026-011</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>32000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
